--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N52_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N52_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>59.68837389954245</v>
+        <v>9.699360758675649</v>
       </c>
       <c r="D2" t="n">
-        <v>32.32874092140987</v>
+        <v>5.253420399729103</v>
       </c>
       <c r="E2" t="n">
-        <v>13.95138964932263</v>
+        <v>2.267100818014928</v>
       </c>
       <c r="F2" t="n">
-        <v>13.03669525570449</v>
+        <v>2.11846297905198</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.49253091410775</v>
+        <v>9.66753627354251</v>
       </c>
       <c r="D3" t="n">
-        <v>24.10911597922516</v>
+        <v>3.917731346624088</v>
       </c>
       <c r="E3" t="n">
-        <v>13.95138964932263</v>
+        <v>2.267100818014928</v>
       </c>
       <c r="F3" t="n">
-        <v>13.03669525570449</v>
+        <v>2.11846297905198</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>60.17798917253911</v>
+        <v>9.778923240537607</v>
       </c>
       <c r="D4" t="n">
-        <v>15.67184453158925</v>
+        <v>2.546674736383252</v>
       </c>
       <c r="E4" t="n">
-        <v>13.95138964932263</v>
+        <v>2.267100818014928</v>
       </c>
       <c r="F4" t="n">
-        <v>13.03669525570449</v>
+        <v>2.11846297905198</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>51.89992437541117</v>
+        <v>8.433737711004316</v>
       </c>
       <c r="D5" t="n">
-        <v>11.97493162854045</v>
+        <v>1.945926389637824</v>
       </c>
       <c r="E5" t="n">
-        <v>13.95138964932263</v>
+        <v>2.267100818014928</v>
       </c>
       <c r="F5" t="n">
-        <v>13.03669525570449</v>
+        <v>2.11846297905198</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.17436566194392</v>
+        <v>5.878334420065888</v>
       </c>
       <c r="D6" t="n">
-        <v>20.23899543520298</v>
+        <v>3.288836758220485</v>
       </c>
       <c r="E6" t="n">
-        <v>13.95138964932263</v>
+        <v>2.267100818014928</v>
       </c>
       <c r="F6" t="n">
-        <v>13.03669525570449</v>
+        <v>2.11846297905198</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.22215368466182</v>
+        <v>5.073599973757546</v>
       </c>
       <c r="D7" t="n">
-        <v>24.88296172446605</v>
+        <v>4.043481280225733</v>
       </c>
       <c r="E7" t="n">
-        <v>13.95138964932263</v>
+        <v>2.267100818014928</v>
       </c>
       <c r="F7" t="n">
-        <v>13.03669525570449</v>
+        <v>2.11846297905198</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>58.87886042247057</v>
+        <v>9.567814818651469</v>
       </c>
       <c r="D8" t="n">
-        <v>33.98031513777898</v>
+        <v>5.521801209889085</v>
       </c>
       <c r="E8" t="n">
-        <v>13.95138964932263</v>
+        <v>2.267100818014928</v>
       </c>
       <c r="F8" t="n">
-        <v>13.03669525570449</v>
+        <v>2.11846297905198</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>13.20268688528783</v>
+        <v>2.145436618859272</v>
       </c>
       <c r="D9" t="n">
-        <v>11.04017731365789</v>
+        <v>1.794028813469407</v>
       </c>
       <c r="E9" t="n">
-        <v>13.95138964932263</v>
+        <v>2.267100818014928</v>
       </c>
       <c r="F9" t="n">
-        <v>13.03669525570449</v>
+        <v>2.11846297905198</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>51.7647378944145</v>
+        <v>8.411769907842357</v>
       </c>
       <c r="D10" t="n">
-        <v>43.11362760130623</v>
+        <v>7.005964485212263</v>
       </c>
       <c r="E10" t="n">
-        <v>13.95138964932263</v>
+        <v>2.267100818014928</v>
       </c>
       <c r="F10" t="n">
-        <v>13.03669525570449</v>
+        <v>2.11846297905198</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>61.41244056024993</v>
+        <v>9.979521591040614</v>
       </c>
       <c r="D11" t="n">
-        <v>50.07917078469427</v>
+        <v>8.137865252512819</v>
       </c>
       <c r="E11" t="n">
-        <v>13.95138964932263</v>
+        <v>2.267100818014928</v>
       </c>
       <c r="F11" t="n">
-        <v>13.03669525570449</v>
+        <v>2.11846297905198</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>46.87945515544639</v>
+        <v>7.617911462760039</v>
       </c>
       <c r="D12" t="n">
-        <v>48.04708447082676</v>
+        <v>7.807651226509349</v>
       </c>
       <c r="E12" t="n">
-        <v>13.95138964932263</v>
+        <v>2.267100818014928</v>
       </c>
       <c r="F12" t="n">
-        <v>13.03669525570449</v>
+        <v>2.11846297905198</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>28.8157315791154</v>
+        <v>4.682556381606253</v>
       </c>
       <c r="D13" t="n">
-        <v>25.41722628503134</v>
+        <v>4.130299271317593</v>
       </c>
       <c r="E13" t="n">
-        <v>13.95138964932263</v>
+        <v>2.267100818014928</v>
       </c>
       <c r="F13" t="n">
-        <v>13.03669525570449</v>
+        <v>2.11846297905198</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>46.31751596690624</v>
+        <v>7.526596344622264</v>
       </c>
       <c r="D14" t="n">
-        <v>45.67237265733246</v>
+        <v>7.421760556816525</v>
       </c>
       <c r="E14" t="n">
-        <v>13.95138964932263</v>
+        <v>2.267100818014928</v>
       </c>
       <c r="F14" t="n">
-        <v>13.03669525570449</v>
+        <v>2.11846297905198</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>45.49146728200452</v>
+        <v>7.392363433325735</v>
       </c>
       <c r="D15" t="n">
-        <v>42.26232894638665</v>
+        <v>6.867628453787831</v>
       </c>
       <c r="E15" t="n">
-        <v>13.95138964932263</v>
+        <v>2.267100818014928</v>
       </c>
       <c r="F15" t="n">
-        <v>13.03669525570449</v>
+        <v>2.11846297905198</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
